--- a/test/testprotocol/testprotocol.xlsx
+++ b/test/testprotocol/testprotocol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Workspaces\GitHub\QE_ATF\test\testprotocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA62AC9B-C0D4-420E-9072-0502E04DC928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3281B70-1FC2-45AE-B90E-247A2C962147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -129,9 +129,6 @@
     <t>testcase18_parquet_dbtable_match_likeobject</t>
   </si>
   <si>
-    <t>/app/test/results/</t>
-  </si>
-  <si>
     <t>testcase22_bigquery_mysql_match</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
   </si>
   <si>
     <t>testcase30_csv_csv_3mill50cols_content</t>
+  </si>
+  <si>
+    <t>test/results/</t>
   </si>
 </sst>
 </file>
@@ -575,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -591,7 +591,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -645,7 +645,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -656,11 +656,11 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="str">
-        <f t="shared" ref="C2:C26" si="0">_xlfn.CONCAT("/app/test/testcases/",B2,".xlsx")</f>
-        <v>/app/test/testcases/testcase1_parquet_parquet_mismatch.xlsx</v>
+        <f>_xlfn.CONCAT("test/testcases/",B2,".xlsx")</f>
+        <v>test/testcases/testcase1_parquet_parquet_mismatch.xlsx</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -671,11 +671,11 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase2_parquet_parquet_match.xlsx</v>
+        <f t="shared" ref="C3:C31" si="0">_xlfn.CONCAT("test/testcases/",B3,".xlsx")</f>
+        <v>test/testcases/testcase2_parquet_parquet_match.xlsx</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
       </c>
       <c r="C4" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase3_csv_csv_match.xlsx</v>
+        <v>test/testcases/testcase3_csv_csv_match.xlsx</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -702,10 +702,10 @@
       </c>
       <c r="C5" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase4_csv_csv_mismatch.xlsx</v>
+        <v>test/testcases/testcase4_csv_csv_mismatch.xlsx</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -717,10 +717,10 @@
       </c>
       <c r="C6" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase5_csv_parquet_match.xlsx</v>
+        <v>test/testcases/testcase5_csv_parquet_match.xlsx</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -732,10 +732,10 @@
       </c>
       <c r="C7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase6_csv_parquet_mismatch.xlsx</v>
+        <v>test/testcases/testcase6_csv_parquet_mismatch.xlsx</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -747,10 +747,10 @@
       </c>
       <c r="C8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase7_json_json_mismatch.xlsx</v>
+        <v>test/testcases/testcase7_json_json_mismatch.xlsx</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -762,10 +762,10 @@
       </c>
       <c r="C9" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase8_json_json_match.xlsx</v>
+        <v>test/testcases/testcase8_json_json_match.xlsx</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -777,10 +777,10 @@
       </c>
       <c r="C10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase9_json_parquet_match.xlsx</v>
+        <v>test/testcases/testcase9_json_parquet_match.xlsx</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -792,10 +792,10 @@
       </c>
       <c r="C11" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase10_json_parquet_mismatch.xlsx</v>
+        <v>test/testcases/testcase10_json_parquet_mismatch.xlsx</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -807,10 +807,10 @@
       </c>
       <c r="C12" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase11_parquet_parquet_match_manual.xlsx</v>
+        <v>test/testcases/testcase11_parquet_parquet_match_manual.xlsx</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -822,10 +822,10 @@
       </c>
       <c r="C13" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase12_parquet_parquet_mismatch_manual.xlsx</v>
+        <v>test/testcases/testcase12_parquet_parquet_mismatch_manual.xlsx</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -837,10 +837,10 @@
       </c>
       <c r="C14" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase13_csv_parquet_match_manuel.xlsx</v>
+        <v>test/testcases/testcase13_csv_parquet_match_manuel.xlsx</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
       </c>
       <c r="C15" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase14_csv_parquet_mismatch_manual.xlsx</v>
+        <v>test/testcases/testcase14_csv_parquet_mismatch_manual.xlsx</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -867,10 +867,10 @@
       </c>
       <c r="C16" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase15_parquet_parquet_match_likeobject.xlsx</v>
+        <v>test/testcases/testcase15_parquet_parquet_match_likeobject.xlsx</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,10 +882,10 @@
       </c>
       <c r="C17" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase16_parquet_parquet_mismatch_likeobject.xlsx</v>
+        <v>test/testcases/testcase16_parquet_parquet_mismatch_likeobject.xlsx</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -897,10 +897,10 @@
       </c>
       <c r="C18" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase17_dbtable_dbtable_match_likeobject.xlsx</v>
+        <v>test/testcases/testcase17_dbtable_dbtable_match_likeobject.xlsx</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -912,10 +912,10 @@
       </c>
       <c r="C19" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase18_parquet_dbtable_match_likeobject.xlsx</v>
+        <v>test/testcases/testcase18_parquet_dbtable_match_likeobject.xlsx</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -923,14 +923,14 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase19_oracle_mysql_match_manual.xlsx</v>
+        <v>test/testcases/testcase19_oracle_mysql_match_manual.xlsx</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -938,14 +938,14 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase20_oracle_bigquery_match_manual.xlsx</v>
+        <v>test/testcases/testcase20_oracle_bigquery_match_manual.xlsx</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -953,14 +953,14 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase21_mysql_csv_match.xlsx</v>
+        <v>test/testcases/testcase21_mysql_csv_match.xlsx</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -968,14 +968,14 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase22_bigquery_mysql_match.xlsx</v>
+        <v>test/testcases/testcase22_bigquery_mysql_match.xlsx</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -983,14 +983,14 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase23_parquet_snowflake_mismatch.xlsx</v>
+        <v>test/testcases/testcase23_parquet_snowflake_mismatch.xlsx</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -998,14 +998,14 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase24_postgres_csv_counting.xlsx</v>
+        <v>test/testcases/testcase24_postgres_csv_counting.xlsx</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1013,14 +1013,14 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>/app/test/testcases/testcase25_oracle_oracle_etljob.xlsx</v>
+        <v>test/testcases/testcase25_oracle_oracle_etljob.xlsx</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1028,14 +1028,14 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="4" t="str">
-        <f>_xlfn.CONCAT("/app/test/testcases/",B27,".xlsx")</f>
-        <v>/app/test/testcases/testcase26_names_fullname_etljob.xlsx</v>
+        <f t="shared" si="0"/>
+        <v>test/testcases/testcase26_names_fullname_etljob.xlsx</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1043,14 +1043,14 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="4" t="str">
-        <f>_xlfn.CONCAT("/app/test/testcases/",B28,".xlsx")</f>
-        <v>/app/test/testcases/testcase27_csv_csv_bigdata_match.xlsx</v>
+        <f t="shared" si="0"/>
+        <v>test/testcases/testcase27_csv_csv_bigdata_match.xlsx</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1058,14 +1058,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="4" t="str">
-        <f>_xlfn.CONCAT("/app/test/testcases/",B29,".xlsx")</f>
-        <v>/app/test/testcases/testcase28_manual_sql_notifications.xlsx</v>
+        <f t="shared" si="0"/>
+        <v>test/testcases/testcase28_manual_sql_notifications.xlsx</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1073,14 +1073,14 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="4" t="str">
-        <f>_xlfn.CONCAT("/app/test/testcases/",B30,".xlsx")</f>
-        <v>/app/test/testcases/testcase29_manual_sql_fullname.xlsx</v>
+        <f t="shared" si="0"/>
+        <v>test/testcases/testcase29_manual_sql_fullname.xlsx</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1088,14 +1088,14 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4" t="str">
-        <f>_xlfn.CONCAT("/app/test/testcases/",B31,".xlsx")</f>
-        <v>/app/test/testcases/testcase30_csv_csv_3mill50cols_content.xlsx</v>
+        <f t="shared" si="0"/>
+        <v>test/testcases/testcase30_csv_csv_3mill50cols_content.xlsx</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1143,8 +1143,5 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="C27 C22" unlockedFormula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>